--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -3017,7 +3017,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3037,7 +3041,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3055,11 +3059,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -3159,15 +3159,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -3179,7 +3175,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3239,11 +3235,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3581,11 +3581,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3657,15 +3661,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4231,11 +4231,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -4247,7 +4251,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4269,13 +4273,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4311,13 +4315,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4353,13 +4357,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4437,15 +4441,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4521,15 +4521,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -4541,7 +4537,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4563,11 +4559,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4677,11 +4677,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4693,7 +4697,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4719,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4753,15 +4757,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -5129,11 +5129,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5145,7 +5149,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5167,15 +5171,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5323,15 +5323,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -5341,7 +5337,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5361,11 +5361,15 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -5375,11 +5379,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -6087,22 +6087,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -6111,7 +6103,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6133,20 +6125,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -6179,14 +6171,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6217,20 +6217,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -6263,14 +6263,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6279,7 +6287,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6301,22 +6309,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6347,26 +6347,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -6375,7 +6371,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6397,22 +6393,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6493,22 +6493,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6517,7 +6521,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6539,26 +6543,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6589,22 +6589,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6613,7 +6617,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6635,26 +6639,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6685,22 +6685,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6709,7 +6717,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6731,20 +6739,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6777,20 +6785,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6823,22 +6831,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6847,7 +6863,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6869,20 +6885,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6915,27 +6931,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6969,20 +6985,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -7015,20 +7031,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -7061,20 +7077,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7107,30 +7123,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -7139,7 +7147,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7161,20 +7169,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -7253,30 +7261,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -8285,11 +8285,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8309,7 +8305,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8323,7 +8319,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8951,15 +8951,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8969,7 +8965,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9027,11 +9027,15 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -9041,11 +9045,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9457,13 +9457,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9617,13 +9617,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
@@ -9659,18 +9659,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9679,7 +9683,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9701,22 +9705,18 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9747,20 +9747,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9793,20 +9793,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9839,20 +9839,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -9931,20 +9931,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9977,18 +9977,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
@@ -9997,7 +10001,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -10019,22 +10023,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T15:16:11.014744</t>
+          <t>生成时间: 2026-06-12T16:09:12.683764</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
+++ b/outputs/week2_excel/603418_友升股份_三表抽取.xlsx
@@ -3079,11 +3079,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3155,15 +3159,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3657,11 +3657,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3695,7 +3699,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3733,15 +3737,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -4231,13 +4231,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -4273,11 +4273,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -4289,7 +4293,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4311,13 +4315,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -4353,13 +4357,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -4395,13 +4399,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -4437,13 +4441,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -4479,15 +4483,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -5087,15 +5087,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -5107,7 +5103,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5129,11 +5125,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -6087,14 +6087,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -6103,7 +6111,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6125,22 +6133,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6171,22 +6171,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -6195,7 +6187,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6217,20 +6209,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -6263,14 +6255,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6347,20 +6347,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -6393,22 +6393,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -6417,7 +6421,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6439,26 +6443,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6489,22 +6489,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -6513,7 +6517,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6535,23 +6539,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -6585,26 +6589,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6685,20 +6685,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6731,20 +6731,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6777,20 +6777,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6823,20 +6823,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6869,30 +6869,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6901,7 +6893,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6923,27 +6915,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6977,20 +6969,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -7023,22 +7015,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7069,20 +7069,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7115,27 +7115,27 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>1680.0</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7169,20 +7169,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -7215,20 +7215,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -7261,20 +7261,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -8475,11 +8475,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8499,7 +8495,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -8537,7 +8533,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -8551,7 +8547,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9457,13 +9457,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9499,15 +9499,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
@@ -9519,7 +9515,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9579,11 +9575,15 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -9659,22 +9659,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9683,7 +9679,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9705,20 +9701,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -9751,20 +9747,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9797,18 +9793,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9839,18 +9839,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9859,7 +9863,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9881,22 +9885,18 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9927,20 +9927,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9973,20 +9973,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -10019,20 +10019,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:05:42.663288</t>
+          <t>生成时间: 2026-06-12T17:10:43.373660</t>
         </is>
       </c>
     </row>
